--- a/004_SapAriba_Target_Dispatcher/lib/net45/Data/Config.xlsx
+++ b/004_SapAriba_Target_Dispatcher/lib/net45/Data/Config.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\grmusarpadev09\OneDrive - insidemedia.net\Desktop\Linktera\Aniket\004_SapAriba_Target_Dispatcher.1.0.10\lib\net45\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09B3E02E-B7BD-40C7-A986-D0337EEDE672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7730FB2B-B5B1-4B9B-80CB-0517249200E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -210,9 +210,6 @@
     <t>devMailAddress</t>
   </si>
   <si>
-    <t>yalcin.karayilan@linktera.com</t>
-  </si>
-  <si>
     <t>BusinessExceptionLogs</t>
   </si>
   <si>
@@ -331,6 +328,9 @@
   </si>
   <si>
     <t>Description (Assets will always overwrite other config)</t>
+  </si>
+  <si>
+    <t>aniketni@cybage.com</t>
   </si>
 </sst>
 </file>
@@ -388,7 +388,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -399,6 +399,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -417,9 +418,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -457,7 +458,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -563,7 +564,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -705,7 +706,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1016,38 +1017,38 @@
       <c r="A38" t="s">
         <v>56</v>
       </c>
-      <c r="B38" t="s">
-        <v>57</v>
+      <c r="B38" s="6" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="14.25" customHeight="1"/>
     <row r="40" spans="1:9" ht="14.25" customHeight="1"/>
     <row r="41" spans="1:9" s="5" customFormat="1" ht="14.25" customHeight="1">
       <c r="A41" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="14.25" customHeight="1">
       <c r="A42" t="s">
+        <v>58</v>
+      </c>
+      <c r="B42" t="s">
         <v>59</v>
-      </c>
-      <c r="B42" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="14.25" customHeight="1"/>
     <row r="44" spans="1:9" ht="14.25" customHeight="1"/>
     <row r="45" spans="1:9" s="5" customFormat="1" ht="14.25" customHeight="1">
       <c r="A45" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="14.25" customHeight="1">
       <c r="A46" t="s">
+        <v>61</v>
+      </c>
+      <c r="B46" t="s">
         <v>62</v>
-      </c>
-      <c r="B46" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="14.25" customHeight="1"/>
@@ -2067,138 +2068,138 @@
     </row>
     <row r="2" spans="1:26" ht="30">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="45">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="5" spans="1:26" ht="14.25" customHeight="1">
       <c r="A5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" t="s">
         <v>68</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>69</v>
-      </c>
-      <c r="C5" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" t="s">
         <v>71</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>72</v>
-      </c>
-      <c r="C7" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
       <c r="A8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" t="s">
         <v>74</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>75</v>
-      </c>
-      <c r="C8" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
       <c r="A9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" t="s">
         <v>77</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>78</v>
-      </c>
-      <c r="C9" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1">
       <c r="A10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" t="s">
         <v>80</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>81</v>
-      </c>
-      <c r="C10" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1">
       <c r="A11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" t="s">
         <v>83</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>84</v>
-      </c>
-      <c r="C11" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
       <c r="A12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" t="s">
         <v>86</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>87</v>
-      </c>
-      <c r="C12" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="14" spans="1:26" ht="14.25" customHeight="1">
       <c r="A14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="17" spans="1:3" ht="45">
       <c r="A17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B17" t="b">
         <v>0</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1"/>
@@ -3195,13 +3196,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -4232,14 +4233,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c4012d6b-a91c-4ec0-90d0-0537ad76586d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ef49ae6b-e58c-46b9-9be1-3da75242d3af" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4454,21 +4453,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c4012d6b-a91c-4ec0-90d0-0537ad76586d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ef49ae6b-e58c-46b9-9be1-3da75242d3af" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6BAF24C-4C87-4CB4-A3C1-51E93D7FACF9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CDE8327-4F64-4FFD-AAD2-6E125ABC8065}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c4012d6b-a91c-4ec0-90d0-0537ad76586d"/>
-    <ds:schemaRef ds:uri="ef49ae6b-e58c-46b9-9be1-3da75242d3af"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4493,9 +4491,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CDE8327-4F64-4FFD-AAD2-6E125ABC8065}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6BAF24C-4C87-4CB4-A3C1-51E93D7FACF9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c4012d6b-a91c-4ec0-90d0-0537ad76586d"/>
+    <ds:schemaRef ds:uri="ef49ae6b-e58c-46b9-9be1-3da75242d3af"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/004_SapAriba_Target_Dispatcher/lib/net45/Data/Config.xlsx
+++ b/004_SapAriba_Target_Dispatcher/lib/net45/Data/Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\grmusarpadev09\OneDrive - insidemedia.net\Desktop\Linktera\Aniket\004_SapAriba_Target_Dispatcher.1.0.10\lib\net45\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\1UiPath\NA-Automation\USA-Target\004_SapAriba_Target_Dispatcher\lib\net45\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7730FB2B-B5B1-4B9B-80CB-0517249200E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E766737E-4BBA-4E95-BFA1-13D25968715A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="101">
   <si>
     <t>Name</t>
   </si>
@@ -207,137 +207,146 @@
     <t xml:space="preserve">[US AR] SAP Target Dispatcher Bot Status Report </t>
   </si>
   <si>
+    <t>BusinessExceptionLogs</t>
+  </si>
+  <si>
+    <t>noMailFound</t>
+  </si>
+  <si>
+    <t>No mail Found For Target.</t>
+  </si>
+  <si>
+    <t>queueAllColumnName</t>
+  </si>
+  <si>
+    <t>QueueColumnName</t>
+  </si>
+  <si>
+    <t>MEDIA;DATE;PO;BILL;AMOUNT;Comment;DIVISION</t>
+  </si>
+  <si>
+    <t>MaxRetryNumber</t>
+  </si>
+  <si>
+    <t>Must be 0 if working with Orchestrator queues. If &gt; 0, the robot will retry the same transaction which failed with a system exception. Must be an integer value.</t>
+  </si>
+  <si>
+    <t>MaxConsecutiveSystemExceptions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The number of consecutive system exceptions allowed. If MaxConsecutiveSystemExceptions is reached, the job is stopped. To disable this feature, set the value to 0. </t>
+  </si>
+  <si>
+    <t>ExScreenshotsFolderPath</t>
+  </si>
+  <si>
+    <t>Exceptions_Screenshots</t>
+  </si>
+  <si>
+    <t>Where to save exceptions screenshots - can be a full or a relative path.</t>
+  </si>
+  <si>
+    <t>LogMessage_GetTransactionData</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Processing Transaction Number: </t>
+  </si>
+  <si>
+    <t>Static part of logging message. Calling Get Transaction Data.</t>
+  </si>
+  <si>
+    <t>LogMessage_GetTransactionDataError</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error getting transaction data for Transaction Number: </t>
+  </si>
+  <si>
+    <t>Static part of logging message. Error retrieving Transaction Data.</t>
+  </si>
+  <si>
+    <t>LogMessage_Success</t>
+  </si>
+  <si>
+    <t>Transaction Successful.</t>
+  </si>
+  <si>
+    <t>Static part of logging message. Processed Transaction succesful.</t>
+  </si>
+  <si>
+    <t>LogMessage_BusinessRuleException</t>
+  </si>
+  <si>
+    <t>Business rule exception.</t>
+  </si>
+  <si>
+    <t>Static part of logging message. Processed Transaction failed with business exception.</t>
+  </si>
+  <si>
+    <t>LogMessage_ApplicationException</t>
+  </si>
+  <si>
+    <t>System exception.</t>
+  </si>
+  <si>
+    <t>Static part of logging message. Processed Transaction failed with application exception.</t>
+  </si>
+  <si>
+    <t>ExceptionMessage_ConsecutiveErrors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The maximum number of consecutive system exceptions was reached. </t>
+  </si>
+  <si>
+    <t>Error message in case MaxConsecutiveSystemExceptions number is reached.</t>
+  </si>
+  <si>
+    <t>RetryNumberGetTransactionItem</t>
+  </si>
+  <si>
+    <t>The number of times Get Transaction Item activity is retried in case of an exception. Must be an integer &gt;= 1.</t>
+  </si>
+  <si>
+    <t>RetryNumberSetTransactionStatus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The number of times Set transaction status activity is retried in case of an exception. Must be an integer &gt;= 1. </t>
+  </si>
+  <si>
+    <t>ShouldMarkJobAsFaulted</t>
+  </si>
+  <si>
+    <t>Must be TRUE or FALSE. If the value is TRUE and an error occurs in Initialization state or the MaxConsecutiveSystemExceptions is reached, the job is marked as Faulted.</t>
+  </si>
+  <si>
+    <t>Asset</t>
+  </si>
+  <si>
+    <t>OrchestratorAssetFolder</t>
+  </si>
+  <si>
+    <t>Description (Assets will always overwrite other config)</t>
+  </si>
+  <si>
     <t>devMailAddress</t>
   </si>
   <si>
-    <t>BusinessExceptionLogs</t>
-  </si>
-  <si>
-    <t>noMailFound</t>
-  </si>
-  <si>
-    <t>No mail Found For Target.</t>
-  </si>
-  <si>
-    <t>queueAllColumnName</t>
-  </si>
-  <si>
-    <t>QueueColumnName</t>
-  </si>
-  <si>
-    <t>MEDIA;DATE;PO;BILL;AMOUNT;Comment;DIVISION</t>
-  </si>
-  <si>
-    <t>MaxRetryNumber</t>
-  </si>
-  <si>
-    <t>Must be 0 if working with Orchestrator queues. If &gt; 0, the robot will retry the same transaction which failed with a system exception. Must be an integer value.</t>
-  </si>
-  <si>
-    <t>MaxConsecutiveSystemExceptions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The number of consecutive system exceptions allowed. If MaxConsecutiveSystemExceptions is reached, the job is stopped. To disable this feature, set the value to 0. </t>
-  </si>
-  <si>
-    <t>ExScreenshotsFolderPath</t>
-  </si>
-  <si>
-    <t>Exceptions_Screenshots</t>
-  </si>
-  <si>
-    <t>Where to save exceptions screenshots - can be a full or a relative path.</t>
-  </si>
-  <si>
-    <t>LogMessage_GetTransactionData</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Processing Transaction Number: </t>
-  </si>
-  <si>
-    <t>Static part of logging message. Calling Get Transaction Data.</t>
-  </si>
-  <si>
-    <t>LogMessage_GetTransactionDataError</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error getting transaction data for Transaction Number: </t>
-  </si>
-  <si>
-    <t>Static part of logging message. Error retrieving Transaction Data.</t>
-  </si>
-  <si>
-    <t>LogMessage_Success</t>
-  </si>
-  <si>
-    <t>Transaction Successful.</t>
-  </si>
-  <si>
-    <t>Static part of logging message. Processed Transaction succesful.</t>
-  </si>
-  <si>
-    <t>LogMessage_BusinessRuleException</t>
-  </si>
-  <si>
-    <t>Business rule exception.</t>
-  </si>
-  <si>
-    <t>Static part of logging message. Processed Transaction failed with business exception.</t>
-  </si>
-  <si>
-    <t>LogMessage_ApplicationException</t>
-  </si>
-  <si>
-    <t>System exception.</t>
-  </si>
-  <si>
-    <t>Static part of logging message. Processed Transaction failed with application exception.</t>
-  </si>
-  <si>
-    <t>ExceptionMessage_ConsecutiveErrors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The maximum number of consecutive system exceptions was reached. </t>
-  </si>
-  <si>
-    <t>Error message in case MaxConsecutiveSystemExceptions number is reached.</t>
-  </si>
-  <si>
-    <t>RetryNumberGetTransactionItem</t>
-  </si>
-  <si>
-    <t>The number of times Get Transaction Item activity is retried in case of an exception. Must be an integer &gt;= 1.</t>
-  </si>
-  <si>
-    <t>RetryNumberSetTransactionStatus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The number of times Set transaction status activity is retried in case of an exception. Must be an integer &gt;= 1. </t>
-  </si>
-  <si>
-    <t>ShouldMarkJobAsFaulted</t>
-  </si>
-  <si>
-    <t>Must be TRUE or FALSE. If the value is TRUE and an error occurs in Initialization state or the MaxConsecutiveSystemExceptions is reached, the job is marked as Faulted.</t>
-  </si>
-  <si>
-    <t>Asset</t>
-  </si>
-  <si>
-    <t>OrchestratorAssetFolder</t>
-  </si>
-  <si>
-    <t>Description (Assets will always overwrite other config)</t>
-  </si>
-  <si>
-    <t>aniketni@cybage.com</t>
+    <t>GMUSA_AR_Dispatcher_Mail_To</t>
+  </si>
+  <si>
+    <t>devMailAddress_cc</t>
+  </si>
+  <si>
+    <t>GMUSA_AR_DB_Connection_String</t>
+  </si>
+  <si>
+    <t>GMUSA_AR_DB_DEV_Connection_String</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -360,6 +369,12 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF4E5E65"/>
+      <name val="Roboto"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -399,7 +414,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -897,7 +912,14 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="14.25" customHeight="1"/>
+    <row r="23" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A23" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
     <row r="24" spans="1:9" ht="14.25" customHeight="1">
       <c r="A24" s="5" t="s">
         <v>33</v>
@@ -1005,7 +1027,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="14.25" customHeight="1">
+    <row r="37" spans="1:9">
       <c r="A37" t="s">
         <v>54</v>
       </c>
@@ -1013,42 +1035,33 @@
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A38" t="s">
-        <v>56</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="14.25" customHeight="1"/>
     <row r="40" spans="1:9" ht="14.25" customHeight="1"/>
     <row r="41" spans="1:9" s="5" customFormat="1" ht="14.25" customHeight="1">
       <c r="A41" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="14.25" customHeight="1">
       <c r="A42" t="s">
+        <v>57</v>
+      </c>
+      <c r="B42" t="s">
         <v>58</v>
-      </c>
-      <c r="B42" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="14.25" customHeight="1"/>
     <row r="44" spans="1:9" ht="14.25" customHeight="1"/>
     <row r="45" spans="1:9" s="5" customFormat="1" ht="14.25" customHeight="1">
       <c r="A45" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="14.25" customHeight="1">
       <c r="A46" t="s">
+        <v>60</v>
+      </c>
+      <c r="B46" t="s">
         <v>61</v>
-      </c>
-      <c r="B46" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="14.25" customHeight="1"/>
@@ -2068,138 +2081,138 @@
     </row>
     <row r="2" spans="1:26" ht="30">
       <c r="A2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="45">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="5" spans="1:26" ht="14.25" customHeight="1">
       <c r="A5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" t="s">
         <v>67</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>68</v>
-      </c>
-      <c r="C5" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" t="s">
         <v>70</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>71</v>
-      </c>
-      <c r="C7" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
       <c r="A8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" t="s">
         <v>73</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>74</v>
-      </c>
-      <c r="C8" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
       <c r="A9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" t="s">
         <v>76</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>77</v>
-      </c>
-      <c r="C9" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1">
       <c r="A10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" t="s">
         <v>79</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>80</v>
-      </c>
-      <c r="C10" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1">
       <c r="A11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" t="s">
         <v>82</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>83</v>
-      </c>
-      <c r="C11" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
       <c r="A12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" t="s">
         <v>85</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>86</v>
-      </c>
-      <c r="C12" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="14" spans="1:26" ht="14.25" customHeight="1">
       <c r="A14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="17" spans="1:3" ht="45">
       <c r="A17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B17" t="b">
         <v>0</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1"/>
@@ -3184,8 +3197,8 @@
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="63.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="26" width="65.42578125" customWidth="1"/>
@@ -3196,13 +3209,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -3227,8 +3240,22 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="3" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="2" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="5" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="6" spans="1:26" ht="14.25" customHeight="1"/>
@@ -4242,8 +4269,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010039B5D92226A63A4AA91620FECE37D35A" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="64f2ee82d02d0a359c601115fca937dc">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c4012d6b-a91c-4ec0-90d0-0537ad76586d" xmlns:ns3="ef49ae6b-e58c-46b9-9be1-3da75242d3af" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ed13e69d4878981f4ecda8d064df8c6d" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010039B5D92226A63A4AA91620FECE37D35A" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d40255432343d9758207c18648e5a326">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c4012d6b-a91c-4ec0-90d0-0537ad76586d" xmlns:ns3="ef49ae6b-e58c-46b9-9be1-3da75242d3af" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c599fead97c0ca65b033184e8fb5180a" ns2:_="" ns3:_="">
     <xsd:import namespace="c4012d6b-a91c-4ec0-90d0-0537ad76586d"/>
     <xsd:import namespace="ef49ae6b-e58c-46b9-9be1-3da75242d3af"/>
     <xsd:element name="properties">
@@ -4262,6 +4289,7 @@
                 <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -4310,6 +4338,11 @@
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
         </xsd:sequence>
       </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="19" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ef49ae6b-e58c-46b9-9be1-3da75242d3af" elementFormDefault="qualified">
@@ -4472,7 +4505,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F782A5A2-AD5F-4798-AD5F-0BDE7BE48ED9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{250502C7-66F3-41F2-96C4-96840CEE9DC4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
